--- a/guides/data-migration-stages/toolkit/Data-Migration-Toolkit-WORKED-EXAMPLE.xlsx
+++ b/guides/data-migration-stages/toolkit/Data-Migration-Toolkit-WORKED-EXAMPLE.xlsx
@@ -791,7 +791,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Northwind Care Services moving from CareTrack 4.2 (legacy) to Meridian Care Platform. Seven years of records plus paper files. Kickoff 02 March 2026, currently mid cutover.</t>
+          <t>Northwind Care Services moving from CareTrack 4.2 (legacy) to Meridian Care Platform. Seven years of records plus paper files. Kickoff 23 February 2026, currently mid cutover.</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
         </is>
       </c>
       <c r="F2" s="19" t="n">
-        <v>46101</v>
+        <v>46094</v>
       </c>
       <c r="G2" s="17" t="inlineStr">
         <is>
@@ -936,7 +936,7 @@
         </is>
       </c>
       <c r="F3" s="19" t="n">
-        <v>46120</v>
+        <v>46113</v>
       </c>
       <c r="G3" s="17" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
         </is>
       </c>
       <c r="F4" s="19" t="n">
-        <v>46150</v>
+        <v>46143</v>
       </c>
       <c r="G4" s="17" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="F5" s="19" t="n">
-        <v>46181</v>
+        <v>46174</v>
       </c>
       <c r="G5" s="17" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="F6" s="19" t="n">
-        <v>46203</v>
+        <v>46197</v>
       </c>
       <c r="G6" s="17" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         </is>
       </c>
       <c r="F7" s="19" t="n">
-        <v>46223</v>
+        <v>46217</v>
       </c>
       <c r="G7" s="17" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       <c r="F8" s="17" t="n"/>
       <c r="G8" s="17" t="inlineStr">
         <is>
-          <t>Pending. Post-load reconciliation runs to 03 August.</t>
+          <t>Pending. Go-live acceptance meeting 03 August.</t>
         </is>
       </c>
     </row>
@@ -1234,7 +1234,7 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>46083</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="9">
@@ -1273,7 +1273,7 @@
         </is>
       </c>
       <c r="B13" s="11">
-        <f>IFERROR(COUNTIFS('Migration Plan'!$B$2:$B$67,"1.*",'Migration Plan'!$F$2:$F$67,"Done")/COUNTIF('Migration Plan'!$B$2:$B$67,"1.*"),0)</f>
+        <f>IFERROR(COUNTIFS('Migration Plan'!$B$2:$B$69,"1.*",'Migration Plan'!$F$2:$F$69,"Done")/COUNTIF('Migration Plan'!$B$2:$B$69,"1.*"),0)</f>
         <v/>
       </c>
     </row>
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="B14" s="11">
-        <f>IFERROR(COUNTIFS('Migration Plan'!$B$2:$B$67,"2.*",'Migration Plan'!$F$2:$F$67,"Done")/COUNTIF('Migration Plan'!$B$2:$B$67,"2.*"),0)</f>
+        <f>IFERROR(COUNTIFS('Migration Plan'!$B$2:$B$69,"2.*",'Migration Plan'!$F$2:$F$69,"Done")/COUNTIF('Migration Plan'!$B$2:$B$69,"2.*"),0)</f>
         <v/>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
         </is>
       </c>
       <c r="B15" s="11">
-        <f>IFERROR(COUNTIFS('Migration Plan'!$B$2:$B$67,"3.*",'Migration Plan'!$F$2:$F$67,"Done")/COUNTIF('Migration Plan'!$B$2:$B$67,"3.*"),0)</f>
+        <f>IFERROR(COUNTIFS('Migration Plan'!$B$2:$B$69,"3.*",'Migration Plan'!$F$2:$F$69,"Done")/COUNTIF('Migration Plan'!$B$2:$B$69,"3.*"),0)</f>
         <v/>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
         </is>
       </c>
       <c r="B16" s="11">
-        <f>IFERROR(COUNTIFS('Migration Plan'!$B$2:$B$67,"4.*",'Migration Plan'!$F$2:$F$67,"Done")/COUNTIF('Migration Plan'!$B$2:$B$67,"4.*"),0)</f>
+        <f>IFERROR(COUNTIFS('Migration Plan'!$B$2:$B$69,"4.*",'Migration Plan'!$F$2:$F$69,"Done")/COUNTIF('Migration Plan'!$B$2:$B$69,"4.*"),0)</f>
         <v/>
       </c>
     </row>
@@ -1317,7 +1317,7 @@
         </is>
       </c>
       <c r="B17" s="11">
-        <f>IFERROR(COUNTIFS('Migration Plan'!$B$2:$B$67,"5.*",'Migration Plan'!$F$2:$F$67,"Done")/COUNTIF('Migration Plan'!$B$2:$B$67,"5.*"),0)</f>
+        <f>IFERROR(COUNTIFS('Migration Plan'!$B$2:$B$69,"5.*",'Migration Plan'!$F$2:$F$69,"Done")/COUNTIF('Migration Plan'!$B$2:$B$69,"5.*"),0)</f>
         <v/>
       </c>
     </row>
@@ -1328,7 +1328,7 @@
         </is>
       </c>
       <c r="B18" s="11">
-        <f>IFERROR(COUNTIFS('Migration Plan'!$B$2:$B$67,"6.*",'Migration Plan'!$F$2:$F$67,"Done")/COUNTIF('Migration Plan'!$B$2:$B$67,"6.*"),0)</f>
+        <f>IFERROR(COUNTIFS('Migration Plan'!$B$2:$B$69,"6.*",'Migration Plan'!$F$2:$F$69,"Done")/COUNTIF('Migration Plan'!$B$2:$B$69,"6.*"),0)</f>
         <v/>
       </c>
     </row>
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="B19" s="11">
-        <f>IFERROR(COUNTIFS('Migration Plan'!$B$2:$B$67,"7.*",'Migration Plan'!$F$2:$F$67,"Done")/COUNTIF('Migration Plan'!$B$2:$B$67,"7.*"),0)</f>
+        <f>IFERROR(COUNTIFS('Migration Plan'!$B$2:$B$69,"7.*",'Migration Plan'!$F$2:$F$69,"Done")/COUNTIF('Migration Plan'!$B$2:$B$69,"7.*"),0)</f>
         <v/>
       </c>
     </row>
@@ -1350,7 +1350,7 @@
         </is>
       </c>
       <c r="B20" s="11">
-        <f>IFERROR(COUNTIFS('Migration Plan'!$B$2:$B$67,"8.*",'Migration Plan'!$F$2:$F$67,"Done")/COUNTIF('Migration Plan'!$B$2:$B$67,"8.*"),0)</f>
+        <f>IFERROR(COUNTIFS('Migration Plan'!$B$2:$B$69,"8.*",'Migration Plan'!$F$2:$F$69,"Done")/COUNTIF('Migration Plan'!$B$2:$B$69,"8.*"),0)</f>
         <v/>
       </c>
     </row>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="B21" s="11">
-        <f>IFERROR(COUNTIFS('Migration Plan'!$B$2:$B$67,"DD.*",'Migration Plan'!$F$2:$F$67,"Done")/COUNTIF('Migration Plan'!$B$2:$B$67,"DD.*"),0)</f>
+        <f>IFERROR(COUNTIFS('Migration Plan'!$B$2:$B$69,"DD.*",'Migration Plan'!$F$2:$F$69,"Done")/COUNTIF('Migration Plan'!$B$2:$B$69,"DD.*"),0)</f>
         <v/>
       </c>
     </row>
@@ -1372,7 +1372,7 @@
         </is>
       </c>
       <c r="B22" s="11">
-        <f>IFERROR(COUNTIFS('Migration Plan'!$B$2:$B$67,"BF.*",'Migration Plan'!$F$2:$F$67,"Done")/COUNTIF('Migration Plan'!$B$2:$B$67,"BF.*"),0)</f>
+        <f>IFERROR(COUNTIFS('Migration Plan'!$B$2:$B$69,"BF.*",'Migration Plan'!$F$2:$F$69,"Done")/COUNTIF('Migration Plan'!$B$2:$B$69,"BF.*"),0)</f>
         <v/>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
         </is>
       </c>
       <c r="B23" s="13">
-        <f>IFERROR(COUNTIF('Migration Plan'!$F$2:$F$67,"Done")/COUNTA('Migration Plan'!$F$2:$F$67),0)</f>
+        <f>IFERROR(COUNTIF('Migration Plan'!$F$2:$F$69,"Done")/COUNTA('Migration Plan'!$F$2:$F$69),0)</f>
         <v/>
       </c>
     </row>
@@ -1405,7 +1405,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N67"/>
+  <dimension ref="A1:N69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1553,10 +1553,10 @@
         <v>1</v>
       </c>
       <c r="H3" s="19" t="n">
-        <v>46084</v>
+        <v>46077</v>
       </c>
       <c r="I3" s="19" t="n">
-        <v>46085</v>
+        <v>46078</v>
       </c>
       <c r="J3" s="17" t="n">
         <v>2</v>
@@ -1607,10 +1607,10 @@
         <v>1</v>
       </c>
       <c r="H4" s="19" t="n">
-        <v>46086</v>
+        <v>46079</v>
       </c>
       <c r="I4" s="19" t="n">
-        <v>46086</v>
+        <v>46079</v>
       </c>
       <c r="J4" s="17" t="n">
         <v>1</v>
@@ -1663,10 +1663,10 @@
         <v>1</v>
       </c>
       <c r="H5" s="19" t="n">
-        <v>46087</v>
+        <v>46080</v>
       </c>
       <c r="I5" s="19" t="n">
-        <v>46090</v>
+        <v>46083</v>
       </c>
       <c r="J5" s="17" t="n">
         <v>2</v>
@@ -1719,10 +1719,10 @@
         <v>1</v>
       </c>
       <c r="H6" s="19" t="n">
-        <v>46091</v>
+        <v>46084</v>
       </c>
       <c r="I6" s="19" t="n">
-        <v>46091</v>
+        <v>46084</v>
       </c>
       <c r="J6" s="17" t="n">
         <v>1</v>
@@ -1775,10 +1775,10 @@
         <v>1</v>
       </c>
       <c r="H7" s="19" t="n">
-        <v>46092</v>
+        <v>46085</v>
       </c>
       <c r="I7" s="19" t="n">
-        <v>46094</v>
+        <v>46087</v>
       </c>
       <c r="J7" s="17" t="n">
         <v>3</v>
@@ -1831,10 +1831,10 @@
         <v>1</v>
       </c>
       <c r="H8" s="19" t="n">
-        <v>46097</v>
+        <v>46090</v>
       </c>
       <c r="I8" s="19" t="n">
-        <v>46099</v>
+        <v>46092</v>
       </c>
       <c r="J8" s="17" t="n">
         <v>3</v>
@@ -1887,10 +1887,10 @@
         <v>1</v>
       </c>
       <c r="H9" s="19" t="n">
-        <v>46100</v>
+        <v>46093</v>
       </c>
       <c r="I9" s="19" t="n">
-        <v>46100</v>
+        <v>46093</v>
       </c>
       <c r="J9" s="17" t="n">
         <v>1</v>
@@ -1943,10 +1943,10 @@
         <v>1</v>
       </c>
       <c r="H10" s="23" t="n">
-        <v>46101</v>
+        <v>46094</v>
       </c>
       <c r="I10" s="23" t="n">
-        <v>46101</v>
+        <v>46094</v>
       </c>
       <c r="J10" s="20" t="n">
         <v>1</v>
@@ -2023,10 +2023,10 @@
         <v>1</v>
       </c>
       <c r="H12" s="19" t="n">
-        <v>46104</v>
+        <v>46097</v>
       </c>
       <c r="I12" s="19" t="n">
-        <v>46105</v>
+        <v>46098</v>
       </c>
       <c r="J12" s="17" t="n">
         <v>2</v>
@@ -2077,10 +2077,10 @@
         <v>1</v>
       </c>
       <c r="H13" s="19" t="n">
-        <v>46106</v>
+        <v>46099</v>
       </c>
       <c r="I13" s="19" t="n">
-        <v>46112</v>
+        <v>46105</v>
       </c>
       <c r="J13" s="17" t="n">
         <v>5</v>
@@ -2133,10 +2133,10 @@
         <v>1</v>
       </c>
       <c r="H14" s="19" t="n">
-        <v>46113</v>
+        <v>46106</v>
       </c>
       <c r="I14" s="19" t="n">
-        <v>46115</v>
+        <v>46108</v>
       </c>
       <c r="J14" s="17" t="n">
         <v>3</v>
@@ -2189,10 +2189,10 @@
         <v>1</v>
       </c>
       <c r="H15" s="19" t="n">
-        <v>46118</v>
+        <v>46111</v>
       </c>
       <c r="I15" s="19" t="n">
-        <v>46119</v>
+        <v>46112</v>
       </c>
       <c r="J15" s="17" t="n">
         <v>2</v>
@@ -2245,10 +2245,10 @@
         <v>1</v>
       </c>
       <c r="H16" s="23" t="n">
-        <v>46120</v>
+        <v>46113</v>
       </c>
       <c r="I16" s="23" t="n">
-        <v>46120</v>
+        <v>46113</v>
       </c>
       <c r="J16" s="20" t="n">
         <v>1</v>
@@ -2325,10 +2325,10 @@
         <v>1</v>
       </c>
       <c r="H18" s="19" t="n">
-        <v>46121</v>
+        <v>46114</v>
       </c>
       <c r="I18" s="19" t="n">
-        <v>46132</v>
+        <v>46125</v>
       </c>
       <c r="J18" s="17" t="n">
         <v>8</v>
@@ -2379,10 +2379,10 @@
         <v>1</v>
       </c>
       <c r="H19" s="19" t="n">
-        <v>46133</v>
+        <v>46126</v>
       </c>
       <c r="I19" s="19" t="n">
-        <v>46136</v>
+        <v>46129</v>
       </c>
       <c r="J19" s="17" t="n">
         <v>4</v>
@@ -2435,10 +2435,10 @@
         <v>1</v>
       </c>
       <c r="H20" s="19" t="n">
-        <v>46139</v>
+        <v>46132</v>
       </c>
       <c r="I20" s="19" t="n">
-        <v>46141</v>
+        <v>46134</v>
       </c>
       <c r="J20" s="17" t="n">
         <v>3</v>
@@ -2491,10 +2491,10 @@
         <v>1</v>
       </c>
       <c r="H21" s="19" t="n">
-        <v>46142</v>
+        <v>46135</v>
       </c>
       <c r="I21" s="19" t="n">
-        <v>46146</v>
+        <v>46139</v>
       </c>
       <c r="J21" s="17" t="n">
         <v>3</v>
@@ -2547,10 +2547,10 @@
         <v>1</v>
       </c>
       <c r="H22" s="19" t="n">
-        <v>46147</v>
+        <v>46140</v>
       </c>
       <c r="I22" s="19" t="n">
-        <v>46149</v>
+        <v>46142</v>
       </c>
       <c r="J22" s="17" t="n">
         <v>3</v>
@@ -2603,10 +2603,10 @@
         <v>1</v>
       </c>
       <c r="H23" s="23" t="n">
-        <v>46150</v>
+        <v>46143</v>
       </c>
       <c r="I23" s="23" t="n">
-        <v>46150</v>
+        <v>46143</v>
       </c>
       <c r="J23" s="20" t="n">
         <v>1</v>
@@ -2683,10 +2683,10 @@
         <v>1</v>
       </c>
       <c r="H25" s="19" t="n">
-        <v>46153</v>
+        <v>46146</v>
       </c>
       <c r="I25" s="19" t="n">
-        <v>46156</v>
+        <v>46149</v>
       </c>
       <c r="J25" s="17" t="n">
         <v>4</v>
@@ -2737,10 +2737,10 @@
         <v>1</v>
       </c>
       <c r="H26" s="19" t="n">
-        <v>46157</v>
+        <v>46150</v>
       </c>
       <c r="I26" s="19" t="n">
-        <v>46161</v>
+        <v>46154</v>
       </c>
       <c r="J26" s="17" t="n">
         <v>3</v>
@@ -2793,10 +2793,10 @@
         <v>1</v>
       </c>
       <c r="H27" s="19" t="n">
-        <v>46162</v>
+        <v>46155</v>
       </c>
       <c r="I27" s="19" t="n">
-        <v>46167</v>
+        <v>46160</v>
       </c>
       <c r="J27" s="17" t="n">
         <v>4</v>
@@ -2849,10 +2849,10 @@
         <v>1</v>
       </c>
       <c r="H28" s="19" t="n">
-        <v>46168</v>
+        <v>46161</v>
       </c>
       <c r="I28" s="19" t="n">
-        <v>46170</v>
+        <v>46163</v>
       </c>
       <c r="J28" s="17" t="n">
         <v>3</v>
@@ -2905,10 +2905,10 @@
         <v>1</v>
       </c>
       <c r="H29" s="19" t="n">
+        <v>46164</v>
+      </c>
+      <c r="I29" s="19" t="n">
         <v>46171</v>
-      </c>
-      <c r="I29" s="19" t="n">
-        <v>46178</v>
       </c>
       <c r="J29" s="17" t="n">
         <v>6</v>
@@ -2961,10 +2961,10 @@
         <v>1</v>
       </c>
       <c r="H30" s="23" t="n">
-        <v>46181</v>
+        <v>46174</v>
       </c>
       <c r="I30" s="23" t="n">
-        <v>46181</v>
+        <v>46174</v>
       </c>
       <c r="J30" s="20" t="n">
         <v>1</v>
@@ -3041,10 +3041,10 @@
         <v>1</v>
       </c>
       <c r="H32" s="19" t="n">
-        <v>46182</v>
+        <v>46175</v>
       </c>
       <c r="I32" s="19" t="n">
-        <v>46185</v>
+        <v>46178</v>
       </c>
       <c r="J32" s="17" t="n">
         <v>4</v>
@@ -3073,7 +3073,7 @@
       </c>
       <c r="C33" s="17" t="inlineStr">
         <is>
-          <t>Run the four checks</t>
+          <t>Run the six checks</t>
         </is>
       </c>
       <c r="D33" s="17" t="inlineStr">
@@ -3095,20 +3095,20 @@
         <v>1</v>
       </c>
       <c r="H33" s="19" t="n">
-        <v>46188</v>
+        <v>46181</v>
       </c>
       <c r="I33" s="19" t="n">
-        <v>46190</v>
+        <v>46184</v>
       </c>
       <c r="J33" s="17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K33" s="17" t="n">
         <v>26</v>
       </c>
       <c r="L33" s="17" t="inlineStr">
         <is>
-          <t>Counts, control totals, links, spot fidelity</t>
+          <t>Counts, control totals, links, spot fidelity, processability, integration</t>
         </is>
       </c>
       <c r="M33" s="17" t="inlineStr">
@@ -3151,10 +3151,10 @@
         <v>1</v>
       </c>
       <c r="H34" s="19" t="n">
-        <v>46191</v>
+        <v>46185</v>
       </c>
       <c r="I34" s="19" t="n">
-        <v>46195</v>
+        <v>46189</v>
       </c>
       <c r="J34" s="17" t="n">
         <v>3</v>
@@ -3207,10 +3207,10 @@
         <v>1</v>
       </c>
       <c r="H35" s="19" t="n">
+        <v>46190</v>
+      </c>
+      <c r="I35" s="19" t="n">
         <v>46196</v>
-      </c>
-      <c r="I35" s="19" t="n">
-        <v>46202</v>
       </c>
       <c r="J35" s="17" t="n">
         <v>5</v>
@@ -3263,10 +3263,10 @@
         <v>1</v>
       </c>
       <c r="H36" s="23" t="n">
-        <v>46203</v>
+        <v>46197</v>
       </c>
       <c r="I36" s="23" t="n">
-        <v>46203</v>
+        <v>46197</v>
       </c>
       <c r="J36" s="20" t="n">
         <v>1</v>
@@ -3343,10 +3343,10 @@
         <v>1</v>
       </c>
       <c r="H38" s="19" t="n">
-        <v>46204</v>
+        <v>46198</v>
       </c>
       <c r="I38" s="19" t="n">
-        <v>46205</v>
+        <v>46199</v>
       </c>
       <c r="J38" s="17" t="n">
         <v>2</v>
@@ -3397,10 +3397,10 @@
         <v>1</v>
       </c>
       <c r="H39" s="19" t="n">
-        <v>46206</v>
+        <v>46202</v>
       </c>
       <c r="I39" s="19" t="n">
-        <v>46210</v>
+        <v>46204</v>
       </c>
       <c r="J39" s="17" t="n">
         <v>3</v>
@@ -3453,10 +3453,10 @@
         <v>1</v>
       </c>
       <c r="H40" s="19" t="n">
+        <v>46205</v>
+      </c>
+      <c r="I40" s="19" t="n">
         <v>46211</v>
-      </c>
-      <c r="I40" s="19" t="n">
-        <v>46217</v>
       </c>
       <c r="J40" s="17" t="n">
         <v>5</v>
@@ -3509,10 +3509,10 @@
         <v>1</v>
       </c>
       <c r="H41" s="19" t="n">
-        <v>46218</v>
+        <v>46212</v>
       </c>
       <c r="I41" s="19" t="n">
-        <v>46220</v>
+        <v>46216</v>
       </c>
       <c r="J41" s="17" t="n">
         <v>3</v>
@@ -3565,10 +3565,10 @@
         <v>1</v>
       </c>
       <c r="H42" s="23" t="n">
-        <v>46223</v>
+        <v>46217</v>
       </c>
       <c r="I42" s="23" t="n">
-        <v>46223</v>
+        <v>46217</v>
       </c>
       <c r="J42" s="20" t="n">
         <v>1</v>
@@ -3645,10 +3645,10 @@
         <v>1</v>
       </c>
       <c r="H44" s="19" t="n">
-        <v>46224</v>
+        <v>46218</v>
       </c>
       <c r="I44" s="19" t="n">
-        <v>46225</v>
+        <v>46219</v>
       </c>
       <c r="J44" s="17" t="n">
         <v>2</v>
@@ -3677,7 +3677,7 @@
       </c>
       <c r="C45" s="17" t="inlineStr">
         <is>
-          <t>Take the final delta export</t>
+          <t>Full cutover rehearsal, timed against the freeze window</t>
         </is>
       </c>
       <c r="D45" s="17" t="inlineStr">
@@ -3687,7 +3687,7 @@
       </c>
       <c r="E45" s="17" t="inlineStr">
         <is>
-          <t>Client IT</t>
+          <t>Migration Lead</t>
         </is>
       </c>
       <c r="F45" s="17" t="inlineStr">
@@ -3699,20 +3699,20 @@
         <v>1</v>
       </c>
       <c r="H45" s="19" t="n">
-        <v>46226</v>
+        <v>46220</v>
       </c>
       <c r="I45" s="19" t="n">
-        <v>46226</v>
+        <v>46224</v>
       </c>
       <c r="J45" s="17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K45" s="17" t="n">
         <v>36</v>
       </c>
       <c r="L45" s="17" t="inlineStr">
         <is>
-          <t>Everything added since the initial export</t>
+          <t>The whole sequence run end to end, clock running. Proves it fits.</t>
         </is>
       </c>
       <c r="M45" s="17" t="inlineStr">
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C46" s="17" t="inlineStr">
         <is>
-          <t>Cutover, in order</t>
+          <t>Take the final delta export</t>
         </is>
       </c>
       <c r="D46" s="17" t="inlineStr">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="E46" s="17" t="inlineStr">
         <is>
-          <t>Migration Lead</t>
+          <t>Client IT</t>
         </is>
       </c>
       <c r="F46" s="17" t="inlineStr">
@@ -3755,20 +3755,20 @@
         <v>1</v>
       </c>
       <c r="H46" s="19" t="n">
-        <v>46227</v>
+        <v>46225</v>
       </c>
       <c r="I46" s="19" t="n">
-        <v>46230</v>
+        <v>46225</v>
       </c>
       <c r="J46" s="17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K46" s="17" t="n">
         <v>37</v>
       </c>
       <c r="L46" s="17" t="inlineStr">
         <is>
-          <t>Records, then documents, then links</t>
+          <t>Everything added since the initial export</t>
         </is>
       </c>
       <c r="M46" s="17" t="inlineStr">
@@ -3789,7 +3789,7 @@
       </c>
       <c r="C47" s="17" t="inlineStr">
         <is>
-          <t>Bridge import</t>
+          <t>Go / no-go decision, with the fallback position named</t>
         </is>
       </c>
       <c r="D47" s="17" t="inlineStr">
@@ -3799,7 +3799,7 @@
       </c>
       <c r="E47" s="17" t="inlineStr">
         <is>
-          <t>Migration Lead</t>
+          <t>Client PM</t>
         </is>
       </c>
       <c r="F47" s="17" t="inlineStr">
@@ -3811,20 +3811,20 @@
         <v>1</v>
       </c>
       <c r="H47" s="19" t="n">
-        <v>46231</v>
+        <v>46226</v>
       </c>
       <c r="I47" s="19" t="n">
-        <v>46232</v>
+        <v>46226</v>
       </c>
       <c r="J47" s="17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K47" s="17" t="n">
         <v>38</v>
       </c>
       <c r="L47" s="17" t="inlineStr">
         <is>
-          <t>The gap closed, not left for later</t>
+          <t>Who decides, on what evidence, and what happens if it is no</t>
         </is>
       </c>
       <c r="M47" s="17" t="inlineStr">
@@ -3845,7 +3845,7 @@
       </c>
       <c r="C48" s="17" t="inlineStr">
         <is>
-          <t>Post-load reconciliation</t>
+          <t>Cutover, in order</t>
         </is>
       </c>
       <c r="D48" s="17" t="inlineStr">
@@ -3860,17 +3860,17 @@
       </c>
       <c r="F48" s="17" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G48" s="18" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H48" s="19" t="n">
-        <v>46233</v>
+        <v>46227</v>
       </c>
       <c r="I48" s="19" t="n">
-        <v>46234</v>
+        <v>46230</v>
       </c>
       <c r="J48" s="17" t="n">
         <v>2</v>
@@ -3880,7 +3880,7 @@
       </c>
       <c r="L48" s="17" t="inlineStr">
         <is>
-          <t>The same checks as the dry run, on production</t>
+          <t>Records, then documents, then links</t>
         </is>
       </c>
       <c r="M48" s="17" t="inlineStr">
@@ -3891,194 +3891,196 @@
       <c r="N48" s="17" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="20" t="n">
+      <c r="A49" s="17" t="n">
         <v>41</v>
       </c>
-      <c r="B49" s="20" t="inlineStr">
+      <c r="B49" s="17" t="inlineStr">
         <is>
           <t>7.6</t>
         </is>
       </c>
-      <c r="C49" s="21" t="inlineStr">
+      <c r="C49" s="17" t="inlineStr">
+        <is>
+          <t>Bridge import</t>
+        </is>
+      </c>
+      <c r="D49" s="17" t="inlineStr">
+        <is>
+          <t>Stage 7 — Freeze, Cutover and Bridge</t>
+        </is>
+      </c>
+      <c r="E49" s="17" t="inlineStr">
+        <is>
+          <t>Migration Lead</t>
+        </is>
+      </c>
+      <c r="F49" s="17" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G49" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H49" s="19" t="n">
+        <v>46231</v>
+      </c>
+      <c r="I49" s="19" t="n">
+        <v>46232</v>
+      </c>
+      <c r="J49" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K49" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="L49" s="17" t="inlineStr">
+        <is>
+          <t>The gap closed, not left for later</t>
+        </is>
+      </c>
+      <c r="M49" s="17" t="inlineStr">
+        <is>
+          <t>migration-cutover</t>
+        </is>
+      </c>
+      <c r="N49" s="17" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="17" t="n">
+        <v>42</v>
+      </c>
+      <c r="B50" s="17" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="C50" s="17" t="inlineStr">
+        <is>
+          <t>Post-load reconciliation</t>
+        </is>
+      </c>
+      <c r="D50" s="17" t="inlineStr">
+        <is>
+          <t>Stage 7 — Freeze, Cutover and Bridge</t>
+        </is>
+      </c>
+      <c r="E50" s="17" t="inlineStr">
+        <is>
+          <t>Migration Lead</t>
+        </is>
+      </c>
+      <c r="F50" s="17" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="G50" s="18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H50" s="19" t="n">
+        <v>46233</v>
+      </c>
+      <c r="I50" s="19" t="n">
+        <v>46234</v>
+      </c>
+      <c r="J50" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K50" s="17" t="n">
+        <v>41</v>
+      </c>
+      <c r="L50" s="17" t="inlineStr">
+        <is>
+          <t>The same six checks as the dry run, on production</t>
+        </is>
+      </c>
+      <c r="M50" s="17" t="inlineStr">
+        <is>
+          <t>migration-cutover</t>
+        </is>
+      </c>
+      <c r="N50" s="17" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="20" t="n">
+        <v>43</v>
+      </c>
+      <c r="B51" s="20" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="C51" s="21" t="inlineStr">
         <is>
           <t>GATE — go-live accepted</t>
         </is>
       </c>
-      <c r="D49" s="20" t="inlineStr">
+      <c r="D51" s="20" t="inlineStr">
         <is>
           <t>Stage 7 — Freeze, Cutover and Bridge</t>
         </is>
       </c>
-      <c r="E49" s="20" t="inlineStr">
+      <c r="E51" s="20" t="inlineStr">
         <is>
           <t>Client PM</t>
         </is>
       </c>
-      <c r="F49" s="20" t="inlineStr">
+      <c r="F51" s="20" t="inlineStr">
         <is>
           <t>In Progress</t>
         </is>
       </c>
-      <c r="G49" s="22" t="n">
+      <c r="G51" s="22" t="n">
         <v>0.5</v>
       </c>
-      <c r="H49" s="23" t="n">
+      <c r="H51" s="23" t="n">
         <v>46237</v>
       </c>
-      <c r="I49" s="23" t="n">
+      <c r="I51" s="23" t="n">
         <v>46237</v>
       </c>
-      <c r="J49" s="20" t="n">
+      <c r="J51" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="K49" s="20" t="n">
-        <v>40</v>
-      </c>
-      <c r="L49" s="20" t="inlineStr">
+      <c r="K51" s="20" t="n">
+        <v>42</v>
+      </c>
+      <c r="L51" s="20" t="inlineStr">
         <is>
           <t>Numbers match, client accepts, together</t>
         </is>
       </c>
-      <c r="M49" s="20" t="inlineStr">
+      <c r="M51" s="20" t="inlineStr">
         <is>
           <t>migration-cutover</t>
         </is>
       </c>
-      <c r="N49" s="20" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="16" t="inlineStr"/>
-      <c r="B50" s="16" t="inlineStr">
+      <c r="N51" s="20" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="16" t="inlineStr"/>
+      <c r="B52" s="16" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="C50" s="16" t="inlineStr">
+      <c r="C52" s="16" t="inlineStr">
         <is>
           <t>Stage 8 — Hypercare and Close</t>
         </is>
       </c>
-      <c r="D50" s="16" t="inlineStr"/>
-      <c r="E50" s="16" t="inlineStr"/>
-      <c r="F50" s="16" t="inlineStr"/>
-      <c r="G50" s="16" t="inlineStr"/>
-      <c r="H50" s="16" t="inlineStr"/>
-      <c r="I50" s="16" t="inlineStr"/>
-      <c r="J50" s="16" t="inlineStr"/>
-      <c r="K50" s="16" t="inlineStr"/>
-      <c r="L50" s="16" t="inlineStr"/>
-      <c r="M50" s="16" t="inlineStr"/>
-      <c r="N50" s="16" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="17" t="n">
-        <v>42</v>
-      </c>
-      <c r="B51" s="17" t="inlineStr">
-        <is>
-          <t>8.1</t>
-        </is>
-      </c>
-      <c r="C51" s="17" t="inlineStr">
-        <is>
-          <t>Agree the hypercare window before you need it</t>
-        </is>
-      </c>
-      <c r="D51" s="17" t="inlineStr">
-        <is>
-          <t>Stage 8 — Hypercare and Close</t>
-        </is>
-      </c>
-      <c r="E51" s="17" t="inlineStr">
-        <is>
-          <t>Client PM</t>
-        </is>
-      </c>
-      <c r="F51" s="17" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="G51" s="18" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="H51" s="19" t="n">
-        <v>46238</v>
-      </c>
-      <c r="I51" s="19" t="n">
-        <v>46238</v>
-      </c>
-      <c r="J51" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K51" s="17" t="inlineStr"/>
-      <c r="L51" s="17" t="inlineStr">
-        <is>
-          <t>Length and route agreed in advance</t>
-        </is>
-      </c>
-      <c r="M51" s="17" t="inlineStr">
-        <is>
-          <t>migration-hypercare</t>
-        </is>
-      </c>
-      <c r="N51" s="17" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="17" t="n">
-        <v>43</v>
-      </c>
-      <c r="B52" s="17" t="inlineStr">
-        <is>
-          <t>8.2</t>
-        </is>
-      </c>
-      <c r="C52" s="17" t="inlineStr">
-        <is>
-          <t>Log and resolve what surfaces</t>
-        </is>
-      </c>
-      <c r="D52" s="17" t="inlineStr">
-        <is>
-          <t>Stage 8 — Hypercare and Close</t>
-        </is>
-      </c>
-      <c r="E52" s="17" t="inlineStr">
-        <is>
-          <t>Migration Lead</t>
-        </is>
-      </c>
-      <c r="F52" s="17" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="G52" s="18" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="H52" s="19" t="n">
-        <v>46239</v>
-      </c>
-      <c r="I52" s="19" t="n">
-        <v>46259</v>
-      </c>
-      <c r="J52" s="17" t="n">
-        <v>15</v>
-      </c>
-      <c r="K52" s="17" t="n">
-        <v>42</v>
-      </c>
-      <c r="L52" s="17" t="inlineStr">
-        <is>
-          <t>The long tail, tracked not absorbed</t>
-        </is>
-      </c>
-      <c r="M52" s="17" t="inlineStr">
-        <is>
-          <t>migration-hypercare</t>
-        </is>
-      </c>
-      <c r="N52" s="17" t="inlineStr"/>
+      <c r="D52" s="16" t="inlineStr"/>
+      <c r="E52" s="16" t="inlineStr"/>
+      <c r="F52" s="16" t="inlineStr"/>
+      <c r="G52" s="16" t="inlineStr"/>
+      <c r="H52" s="16" t="inlineStr"/>
+      <c r="I52" s="16" t="inlineStr"/>
+      <c r="J52" s="16" t="inlineStr"/>
+      <c r="K52" s="16" t="inlineStr"/>
+      <c r="L52" s="16" t="inlineStr"/>
+      <c r="M52" s="16" t="inlineStr"/>
+      <c r="N52" s="16" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="17" t="n">
@@ -4086,12 +4088,12 @@
       </c>
       <c r="B53" s="17" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="C53" s="17" t="inlineStr">
         <is>
-          <t>Final reconciliation report</t>
+          <t>Agree the hypercare window before you need it</t>
         </is>
       </c>
       <c r="D53" s="17" t="inlineStr">
@@ -4101,32 +4103,30 @@
       </c>
       <c r="E53" s="17" t="inlineStr">
         <is>
-          <t>Migration Lead</t>
+          <t>Client PM</t>
         </is>
       </c>
       <c r="F53" s="17" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G53" s="18" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="H53" s="19" t="n">
-        <v>46260</v>
+        <v>46238</v>
       </c>
       <c r="I53" s="19" t="n">
-        <v>46262</v>
+        <v>46238</v>
       </c>
       <c r="J53" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="K53" s="17" t="n">
-        <v>43</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K53" s="17" t="inlineStr"/>
       <c r="L53" s="17" t="inlineStr">
         <is>
-          <t>The proof the move was complete</t>
+          <t>Length and route agreed in advance</t>
         </is>
       </c>
       <c r="M53" s="17" t="inlineStr">
@@ -4142,12 +4142,12 @@
       </c>
       <c r="B54" s="17" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="C54" s="17" t="inlineStr">
         <is>
-          <t>Internal results readout</t>
+          <t>Log and resolve what surfaces</t>
         </is>
       </c>
       <c r="D54" s="17" t="inlineStr">
@@ -4162,27 +4162,27 @@
       </c>
       <c r="F54" s="17" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G54" s="18" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="H54" s="19" t="n">
-        <v>46265</v>
+        <v>46239</v>
       </c>
       <c r="I54" s="19" t="n">
-        <v>46265</v>
+        <v>46259</v>
       </c>
       <c r="J54" s="17" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="K54" s="17" t="n">
         <v>44</v>
       </c>
       <c r="L54" s="17" t="inlineStr">
         <is>
-          <t>What went well, what to change next time</t>
+          <t>The long tail, tracked not absorbed</t>
         </is>
       </c>
       <c r="M54" s="17" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="B55" s="17" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="C55" s="17" t="inlineStr">
         <is>
-          <t>Handoff to Support</t>
+          <t>Final reconciliation report</t>
         </is>
       </c>
       <c r="D55" s="17" t="inlineStr">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="E55" s="17" t="inlineStr">
         <is>
-          <t>Support / CS</t>
+          <t>Migration Lead</t>
         </is>
       </c>
       <c r="F55" s="17" t="inlineStr">
@@ -4225,218 +4225,220 @@
         <v>0</v>
       </c>
       <c r="H55" s="19" t="n">
-        <v>46266</v>
+        <v>46260</v>
       </c>
       <c r="I55" s="19" t="n">
-        <v>46267</v>
+        <v>46262</v>
       </c>
       <c r="J55" s="17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K55" s="17" t="n">
         <v>45</v>
       </c>
       <c r="L55" s="17" t="inlineStr">
         <is>
+          <t>The proof the move was complete</t>
+        </is>
+      </c>
+      <c r="M55" s="17" t="inlineStr">
+        <is>
+          <t>migration-hypercare</t>
+        </is>
+      </c>
+      <c r="N55" s="17" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="17" t="n">
+        <v>47</v>
+      </c>
+      <c r="B56" s="17" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="C56" s="17" t="inlineStr">
+        <is>
+          <t>Internal results readout</t>
+        </is>
+      </c>
+      <c r="D56" s="17" t="inlineStr">
+        <is>
+          <t>Stage 8 — Hypercare and Close</t>
+        </is>
+      </c>
+      <c r="E56" s="17" t="inlineStr">
+        <is>
+          <t>Migration Lead</t>
+        </is>
+      </c>
+      <c r="F56" s="17" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="G56" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" s="19" t="n">
+        <v>46265</v>
+      </c>
+      <c r="I56" s="19" t="n">
+        <v>46265</v>
+      </c>
+      <c r="J56" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K56" s="17" t="n">
+        <v>46</v>
+      </c>
+      <c r="L56" s="17" t="inlineStr">
+        <is>
+          <t>What went well, what to change next time</t>
+        </is>
+      </c>
+      <c r="M56" s="17" t="inlineStr">
+        <is>
+          <t>migration-hypercare</t>
+        </is>
+      </c>
+      <c r="N56" s="17" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="17" t="n">
+        <v>48</v>
+      </c>
+      <c r="B57" s="17" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="C57" s="17" t="inlineStr">
+        <is>
+          <t>Handoff to Support</t>
+        </is>
+      </c>
+      <c r="D57" s="17" t="inlineStr">
+        <is>
+          <t>Stage 8 — Hypercare and Close</t>
+        </is>
+      </c>
+      <c r="E57" s="17" t="inlineStr">
+        <is>
+          <t>Support / CS</t>
+        </is>
+      </c>
+      <c r="F57" s="17" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="G57" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" s="19" t="n">
+        <v>46266</v>
+      </c>
+      <c r="I57" s="19" t="n">
+        <v>46267</v>
+      </c>
+      <c r="J57" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K57" s="17" t="n">
+        <v>47</v>
+      </c>
+      <c r="L57" s="17" t="inlineStr">
+        <is>
           <t>So it lands warmly, with context</t>
         </is>
       </c>
-      <c r="M55" s="17" t="inlineStr">
+      <c r="M57" s="17" t="inlineStr">
         <is>
           <t>migration-hypercare</t>
         </is>
       </c>
-      <c r="N55" s="17" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="20" t="n">
-        <v>47</v>
-      </c>
-      <c r="B56" s="20" t="inlineStr">
+      <c r="N57" s="17" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="20" t="n">
+        <v>49</v>
+      </c>
+      <c r="B58" s="20" t="inlineStr">
         <is>
           <t>8.6</t>
         </is>
       </c>
-      <c r="C56" s="21" t="inlineStr">
+      <c r="C58" s="21" t="inlineStr">
         <is>
           <t>GATE — project closed, handoff accepted</t>
         </is>
       </c>
-      <c r="D56" s="20" t="inlineStr">
+      <c r="D58" s="20" t="inlineStr">
         <is>
           <t>Stage 8 — Hypercare and Close</t>
         </is>
       </c>
-      <c r="E56" s="20" t="inlineStr">
+      <c r="E58" s="20" t="inlineStr">
         <is>
           <t>Support / CS</t>
         </is>
       </c>
-      <c r="F56" s="20" t="inlineStr">
+      <c r="F58" s="20" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G56" s="22" t="n">
+      <c r="G58" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="H56" s="23" t="n">
+      <c r="H58" s="23" t="n">
         <v>46268</v>
       </c>
-      <c r="I56" s="23" t="n">
+      <c r="I58" s="23" t="n">
         <v>46268</v>
       </c>
-      <c r="J56" s="20" t="n">
+      <c r="J58" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="K56" s="20" t="n">
-        <v>46</v>
-      </c>
-      <c r="L56" s="20" t="inlineStr">
+      <c r="K58" s="20" t="n">
+        <v>48</v>
+      </c>
+      <c r="L58" s="20" t="inlineStr">
         <is>
           <t>Support owns it now, knowingly</t>
         </is>
       </c>
-      <c r="M56" s="20" t="inlineStr">
+      <c r="M58" s="20" t="inlineStr">
         <is>
           <t>migration-hypercare</t>
         </is>
       </c>
-      <c r="N56" s="20" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="16" t="inlineStr"/>
-      <c r="B57" s="16" t="inlineStr">
+      <c r="N58" s="20" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="16" t="inlineStr"/>
+      <c r="B59" s="16" t="inlineStr">
         <is>
           <t>DD</t>
         </is>
       </c>
-      <c r="C57" s="16" t="inlineStr">
+      <c r="C59" s="16" t="inlineStr">
         <is>
           <t>Parallel — Document Digitization</t>
         </is>
       </c>
-      <c r="D57" s="16" t="inlineStr"/>
-      <c r="E57" s="16" t="inlineStr"/>
-      <c r="F57" s="16" t="inlineStr"/>
-      <c r="G57" s="16" t="inlineStr"/>
-      <c r="H57" s="16" t="inlineStr"/>
-      <c r="I57" s="16" t="inlineStr"/>
-      <c r="J57" s="16" t="inlineStr"/>
-      <c r="K57" s="16" t="inlineStr"/>
-      <c r="L57" s="16" t="inlineStr"/>
-      <c r="M57" s="16" t="inlineStr"/>
-      <c r="N57" s="16" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="17" t="n">
-        <v>48</v>
-      </c>
-      <c r="B58" s="17" t="inlineStr">
-        <is>
-          <t>DD.1</t>
-        </is>
-      </c>
-      <c r="C58" s="17" t="inlineStr">
-        <is>
-          <t>Audit paper volume, condition and scope</t>
-        </is>
-      </c>
-      <c r="D58" s="17" t="inlineStr">
-        <is>
-          <t>Parallel — Document Digitization</t>
-        </is>
-      </c>
-      <c r="E58" s="17" t="inlineStr">
-        <is>
-          <t>Client Data Owner</t>
-        </is>
-      </c>
-      <c r="F58" s="17" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="G58" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="H58" s="19" t="n">
-        <v>46087</v>
-      </c>
-      <c r="I58" s="19" t="n">
-        <v>46093</v>
-      </c>
-      <c r="J58" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="K58" s="17" t="inlineStr"/>
-      <c r="L58" s="17" t="inlineStr">
-        <is>
-          <t>How much paper, in what state</t>
-        </is>
-      </c>
-      <c r="M58" s="17" t="inlineStr">
-        <is>
-          <t>migration-field-mapping</t>
-        </is>
-      </c>
-      <c r="N58" s="17" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="17" t="n">
-        <v>49</v>
-      </c>
-      <c r="B59" s="17" t="inlineStr">
-        <is>
-          <t>DD.2</t>
-        </is>
-      </c>
-      <c r="C59" s="17" t="inlineStr">
-        <is>
-          <t>Select vendor and agree chain of custody</t>
-        </is>
-      </c>
-      <c r="D59" s="17" t="inlineStr">
-        <is>
-          <t>Parallel — Document Digitization</t>
-        </is>
-      </c>
-      <c r="E59" s="17" t="inlineStr">
-        <is>
-          <t>Client PM</t>
-        </is>
-      </c>
-      <c r="F59" s="17" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="G59" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="H59" s="19" t="n">
-        <v>46094</v>
-      </c>
-      <c r="I59" s="19" t="n">
-        <v>46105</v>
-      </c>
-      <c r="J59" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="K59" s="17" t="n">
-        <v>48</v>
-      </c>
-      <c r="L59" s="17" t="inlineStr">
-        <is>
-          <t>Who holds the records, and how it is proven</t>
-        </is>
-      </c>
-      <c r="M59" s="17" t="inlineStr">
-        <is>
-          <t>migration-field-mapping</t>
-        </is>
-      </c>
-      <c r="N59" s="17" t="inlineStr"/>
+      <c r="D59" s="16" t="inlineStr"/>
+      <c r="E59" s="16" t="inlineStr"/>
+      <c r="F59" s="16" t="inlineStr"/>
+      <c r="G59" s="16" t="inlineStr"/>
+      <c r="H59" s="16" t="inlineStr"/>
+      <c r="I59" s="16" t="inlineStr"/>
+      <c r="J59" s="16" t="inlineStr"/>
+      <c r="K59" s="16" t="inlineStr"/>
+      <c r="L59" s="16" t="inlineStr"/>
+      <c r="M59" s="16" t="inlineStr"/>
+      <c r="N59" s="16" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="17" t="n">
@@ -4444,12 +4446,12 @@
       </c>
       <c r="B60" s="17" t="inlineStr">
         <is>
-          <t>DD.3</t>
+          <t>DD.1</t>
         </is>
       </c>
       <c r="C60" s="17" t="inlineStr">
         <is>
-          <t>Define indexing metadata to match the map</t>
+          <t>Audit paper volume, condition and scope</t>
         </is>
       </c>
       <c r="D60" s="17" t="inlineStr">
@@ -4459,7 +4461,7 @@
       </c>
       <c r="E60" s="17" t="inlineStr">
         <is>
-          <t>Migration Lead</t>
+          <t>Client Data Owner</t>
         </is>
       </c>
       <c r="F60" s="17" t="inlineStr">
@@ -4471,20 +4473,18 @@
         <v>1</v>
       </c>
       <c r="H60" s="19" t="n">
-        <v>46106</v>
+        <v>46080</v>
       </c>
       <c r="I60" s="19" t="n">
-        <v>46111</v>
+        <v>46086</v>
       </c>
       <c r="J60" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="K60" s="17" t="n">
-        <v>49</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K60" s="17" t="inlineStr"/>
       <c r="L60" s="17" t="inlineStr">
         <is>
-          <t>Index to the target fields, not to what is convenient</t>
+          <t>How much paper, in what state</t>
         </is>
       </c>
       <c r="M60" s="17" t="inlineStr">
@@ -4500,12 +4500,12 @@
       </c>
       <c r="B61" s="17" t="inlineStr">
         <is>
-          <t>DD.4</t>
+          <t>DD.2</t>
         </is>
       </c>
       <c r="C61" s="17" t="inlineStr">
         <is>
-          <t>Scan, OCR, index and QA</t>
+          <t>Select vendor and agree chain of custody</t>
         </is>
       </c>
       <c r="D61" s="17" t="inlineStr">
@@ -4515,7 +4515,7 @@
       </c>
       <c r="E61" s="17" t="inlineStr">
         <is>
-          <t>Scanning Vendor</t>
+          <t>Client PM</t>
         </is>
       </c>
       <c r="F61" s="17" t="inlineStr">
@@ -4527,20 +4527,20 @@
         <v>1</v>
       </c>
       <c r="H61" s="19" t="n">
-        <v>46112</v>
+        <v>46087</v>
       </c>
       <c r="I61" s="19" t="n">
-        <v>46153</v>
+        <v>46098</v>
       </c>
       <c r="J61" s="17" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="K61" s="17" t="n">
         <v>50</v>
       </c>
       <c r="L61" s="17" t="inlineStr">
         <is>
-          <t>Digitized and indexed, ready to link</t>
+          <t>Who holds the records, and how it is proven</t>
         </is>
       </c>
       <c r="M61" s="17" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="B62" s="17" t="inlineStr">
         <is>
-          <t>DD.5</t>
+          <t>DD.3</t>
         </is>
       </c>
       <c r="C62" s="17" t="inlineStr">
         <is>
-          <t>Day-forward scanning live at go-live</t>
+          <t>Define indexing metadata to match the map</t>
         </is>
       </c>
       <c r="D62" s="17" t="inlineStr">
@@ -4571,7 +4571,7 @@
       </c>
       <c r="E62" s="17" t="inlineStr">
         <is>
-          <t>Scanning Vendor</t>
+          <t>Migration Lead</t>
         </is>
       </c>
       <c r="F62" s="17" t="inlineStr">
@@ -4583,162 +4583,164 @@
         <v>1</v>
       </c>
       <c r="H62" s="19" t="n">
-        <v>46154</v>
+        <v>46099</v>
       </c>
       <c r="I62" s="19" t="n">
-        <v>46154</v>
+        <v>46104</v>
       </c>
       <c r="J62" s="17" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K62" s="17" t="n">
         <v>51</v>
       </c>
       <c r="L62" s="17" t="inlineStr">
         <is>
-          <t>New paper never becomes new backlog</t>
+          <t>Index to the target fields, not to what is convenient</t>
         </is>
       </c>
       <c r="M62" s="17" t="inlineStr">
         <is>
-          <t>migration-cutover</t>
+          <t>migration-field-mapping</t>
         </is>
       </c>
       <c r="N62" s="17" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="16" t="inlineStr"/>
-      <c r="B63" s="16" t="inlineStr">
-        <is>
-          <t>BF</t>
-        </is>
-      </c>
-      <c r="C63" s="16" t="inlineStr">
-        <is>
-          <t>Follow-on — Backfile (T plus 6 months)</t>
-        </is>
-      </c>
-      <c r="D63" s="16" t="inlineStr"/>
-      <c r="E63" s="16" t="inlineStr"/>
-      <c r="F63" s="16" t="inlineStr"/>
-      <c r="G63" s="16" t="inlineStr"/>
-      <c r="H63" s="16" t="inlineStr"/>
-      <c r="I63" s="16" t="inlineStr"/>
-      <c r="J63" s="16" t="inlineStr"/>
-      <c r="K63" s="16" t="inlineStr"/>
-      <c r="L63" s="16" t="inlineStr"/>
-      <c r="M63" s="16" t="inlineStr"/>
-      <c r="N63" s="16" t="inlineStr"/>
+      <c r="A63" s="17" t="n">
+        <v>53</v>
+      </c>
+      <c r="B63" s="17" t="inlineStr">
+        <is>
+          <t>DD.4</t>
+        </is>
+      </c>
+      <c r="C63" s="17" t="inlineStr">
+        <is>
+          <t>Scan, OCR, index and QA</t>
+        </is>
+      </c>
+      <c r="D63" s="17" t="inlineStr">
+        <is>
+          <t>Parallel — Document Digitization</t>
+        </is>
+      </c>
+      <c r="E63" s="17" t="inlineStr">
+        <is>
+          <t>Scanning Vendor</t>
+        </is>
+      </c>
+      <c r="F63" s="17" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G63" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H63" s="19" t="n">
+        <v>46105</v>
+      </c>
+      <c r="I63" s="19" t="n">
+        <v>46146</v>
+      </c>
+      <c r="J63" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="K63" s="17" t="n">
+        <v>52</v>
+      </c>
+      <c r="L63" s="17" t="inlineStr">
+        <is>
+          <t>Digitized and indexed, ready to link</t>
+        </is>
+      </c>
+      <c r="M63" s="17" t="inlineStr">
+        <is>
+          <t>migration-field-mapping</t>
+        </is>
+      </c>
+      <c r="N63" s="17" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="17" t="n">
+        <v>54</v>
+      </c>
+      <c r="B64" s="17" t="inlineStr">
+        <is>
+          <t>DD.5</t>
+        </is>
+      </c>
+      <c r="C64" s="17" t="inlineStr">
+        <is>
+          <t>Day-forward scanning live at go-live</t>
+        </is>
+      </c>
+      <c r="D64" s="17" t="inlineStr">
+        <is>
+          <t>Parallel — Document Digitization</t>
+        </is>
+      </c>
+      <c r="E64" s="17" t="inlineStr">
+        <is>
+          <t>Scanning Vendor</t>
+        </is>
+      </c>
+      <c r="F64" s="17" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G64" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H64" s="19" t="n">
+        <v>46147</v>
+      </c>
+      <c r="I64" s="19" t="n">
+        <v>46147</v>
+      </c>
+      <c r="J64" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K64" s="17" t="n">
         <v>53</v>
       </c>
-      <c r="B64" s="17" t="inlineStr">
-        <is>
-          <t>BF.1</t>
-        </is>
-      </c>
-      <c r="C64" s="17" t="inlineStr">
-        <is>
-          <t>Backfile scanning continues</t>
-        </is>
-      </c>
-      <c r="D64" s="17" t="inlineStr">
+      <c r="L64" s="17" t="inlineStr">
+        <is>
+          <t>New paper never becomes new backlog</t>
+        </is>
+      </c>
+      <c r="M64" s="17" t="inlineStr">
+        <is>
+          <t>migration-cutover</t>
+        </is>
+      </c>
+      <c r="N64" s="17" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="16" t="inlineStr"/>
+      <c r="B65" s="16" t="inlineStr">
+        <is>
+          <t>BF</t>
+        </is>
+      </c>
+      <c r="C65" s="16" t="inlineStr">
         <is>
           <t>Follow-on — Backfile (T plus 6 months)</t>
         </is>
       </c>
-      <c r="E64" s="17" t="inlineStr">
-        <is>
-          <t>Scanning Vendor</t>
-        </is>
-      </c>
-      <c r="F64" s="17" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="G64" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H64" s="19" t="n">
-        <v>46269</v>
-      </c>
-      <c r="I64" s="19" t="n">
-        <v>46394</v>
-      </c>
-      <c r="J64" s="17" t="n">
-        <v>90</v>
-      </c>
-      <c r="K64" s="17" t="inlineStr"/>
-      <c r="L64" s="17" t="inlineStr">
-        <is>
-          <t>The historical paper, on contract</t>
-        </is>
-      </c>
-      <c r="M64" s="17" t="inlineStr">
-        <is>
-          <t>migration-hypercare</t>
-        </is>
-      </c>
-      <c r="N64" s="17" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="17" t="n">
-        <v>54</v>
-      </c>
-      <c r="B65" s="17" t="inlineStr">
-        <is>
-          <t>BF.2</t>
-        </is>
-      </c>
-      <c r="C65" s="17" t="inlineStr">
-        <is>
-          <t>Bridge import of historical documents</t>
-        </is>
-      </c>
-      <c r="D65" s="17" t="inlineStr">
-        <is>
-          <t>Follow-on — Backfile (T plus 6 months)</t>
-        </is>
-      </c>
-      <c r="E65" s="17" t="inlineStr">
-        <is>
-          <t>Migration Lead</t>
-        </is>
-      </c>
-      <c r="F65" s="17" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="G65" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H65" s="19" t="n">
-        <v>46395</v>
-      </c>
-      <c r="I65" s="19" t="n">
-        <v>46401</v>
-      </c>
-      <c r="J65" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="K65" s="17" t="n">
-        <v>53</v>
-      </c>
-      <c r="L65" s="17" t="inlineStr">
-        <is>
-          <t>Loaded and linked by the same unique ID</t>
-        </is>
-      </c>
-      <c r="M65" s="17" t="inlineStr">
-        <is>
-          <t>migration-field-mapping</t>
-        </is>
-      </c>
-      <c r="N65" s="17" t="inlineStr"/>
+      <c r="D65" s="16" t="inlineStr"/>
+      <c r="E65" s="16" t="inlineStr"/>
+      <c r="F65" s="16" t="inlineStr"/>
+      <c r="G65" s="16" t="inlineStr"/>
+      <c r="H65" s="16" t="inlineStr"/>
+      <c r="I65" s="16" t="inlineStr"/>
+      <c r="J65" s="16" t="inlineStr"/>
+      <c r="K65" s="16" t="inlineStr"/>
+      <c r="L65" s="16" t="inlineStr"/>
+      <c r="M65" s="16" t="inlineStr"/>
+      <c r="N65" s="16" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="17" t="n">
@@ -4746,12 +4748,12 @@
       </c>
       <c r="B66" s="17" t="inlineStr">
         <is>
-          <t>BF.3</t>
+          <t>BF.1</t>
         </is>
       </c>
       <c r="C66" s="17" t="inlineStr">
         <is>
-          <t>Reconcile the backfile</t>
+          <t>Backfile scanning continues</t>
         </is>
       </c>
       <c r="D66" s="17" t="inlineStr">
@@ -4761,7 +4763,7 @@
       </c>
       <c r="E66" s="17" t="inlineStr">
         <is>
-          <t>Migration Lead</t>
+          <t>Scanning Vendor</t>
         </is>
       </c>
       <c r="F66" s="17" t="inlineStr">
@@ -4773,25 +4775,23 @@
         <v>0</v>
       </c>
       <c r="H66" s="19" t="n">
-        <v>46402</v>
+        <v>46269</v>
       </c>
       <c r="I66" s="19" t="n">
-        <v>46406</v>
+        <v>46394</v>
       </c>
       <c r="J66" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="K66" s="17" t="n">
-        <v>54</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="K66" s="17" t="inlineStr"/>
       <c r="L66" s="17" t="inlineStr">
         <is>
-          <t>Counts tie, no orphans</t>
+          <t>The historical paper, on contract</t>
         </is>
       </c>
       <c r="M66" s="17" t="inlineStr">
         <is>
-          <t>migration-pitfalls</t>
+          <t>migration-hypercare</t>
         </is>
       </c>
       <c r="N66" s="17" t="inlineStr"/>
@@ -4802,12 +4802,12 @@
       </c>
       <c r="B67" s="17" t="inlineStr">
         <is>
-          <t>BF.4</t>
+          <t>BF.2</t>
         </is>
       </c>
       <c r="C67" s="17" t="inlineStr">
         <is>
-          <t>Decommission paper storage</t>
+          <t>Bridge import of historical documents</t>
         </is>
       </c>
       <c r="D67" s="17" t="inlineStr">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="E67" s="17" t="inlineStr">
         <is>
-          <t>Client PM</t>
+          <t>Migration Lead</t>
         </is>
       </c>
       <c r="F67" s="17" t="inlineStr">
@@ -4829,10 +4829,10 @@
         <v>0</v>
       </c>
       <c r="H67" s="19" t="n">
-        <v>46407</v>
+        <v>46395</v>
       </c>
       <c r="I67" s="19" t="n">
-        <v>46413</v>
+        <v>46401</v>
       </c>
       <c r="J67" s="17" t="n">
         <v>5</v>
@@ -4842,19 +4842,131 @@
       </c>
       <c r="L67" s="17" t="inlineStr">
         <is>
+          <t>Loaded and linked by the same unique ID</t>
+        </is>
+      </c>
+      <c r="M67" s="17" t="inlineStr">
+        <is>
+          <t>migration-field-mapping</t>
+        </is>
+      </c>
+      <c r="N67" s="17" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="17" t="n">
+        <v>57</v>
+      </c>
+      <c r="B68" s="17" t="inlineStr">
+        <is>
+          <t>BF.3</t>
+        </is>
+      </c>
+      <c r="C68" s="17" t="inlineStr">
+        <is>
+          <t>Reconcile the backfile</t>
+        </is>
+      </c>
+      <c r="D68" s="17" t="inlineStr">
+        <is>
+          <t>Follow-on — Backfile (T plus 6 months)</t>
+        </is>
+      </c>
+      <c r="E68" s="17" t="inlineStr">
+        <is>
+          <t>Migration Lead</t>
+        </is>
+      </c>
+      <c r="F68" s="17" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="G68" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" s="19" t="n">
+        <v>46402</v>
+      </c>
+      <c r="I68" s="19" t="n">
+        <v>46406</v>
+      </c>
+      <c r="J68" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="K68" s="17" t="n">
+        <v>56</v>
+      </c>
+      <c r="L68" s="17" t="inlineStr">
+        <is>
+          <t>Counts tie, no orphans</t>
+        </is>
+      </c>
+      <c r="M68" s="17" t="inlineStr">
+        <is>
+          <t>migration-pitfalls</t>
+        </is>
+      </c>
+      <c r="N68" s="17" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="17" t="n">
+        <v>58</v>
+      </c>
+      <c r="B69" s="17" t="inlineStr">
+        <is>
+          <t>BF.4</t>
+        </is>
+      </c>
+      <c r="C69" s="17" t="inlineStr">
+        <is>
+          <t>Decommission paper storage</t>
+        </is>
+      </c>
+      <c r="D69" s="17" t="inlineStr">
+        <is>
+          <t>Follow-on — Backfile (T plus 6 months)</t>
+        </is>
+      </c>
+      <c r="E69" s="17" t="inlineStr">
+        <is>
+          <t>Client PM</t>
+        </is>
+      </c>
+      <c r="F69" s="17" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="G69" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" s="19" t="n">
+        <v>46407</v>
+      </c>
+      <c r="I69" s="19" t="n">
+        <v>46413</v>
+      </c>
+      <c r="J69" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="K69" s="17" t="n">
+        <v>57</v>
+      </c>
+      <c r="L69" s="17" t="inlineStr">
+        <is>
           <t>The reason the project was funded</t>
         </is>
       </c>
-      <c r="M67" s="17" t="inlineStr">
+      <c r="M69" s="17" t="inlineStr">
         <is>
           <t>migration-hypercare</t>
         </is>
       </c>
-      <c r="N67" s="17" t="inlineStr"/>
+      <c r="N69" s="17" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="F2:F67" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F2:F69" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Not Started,In Progress,Done,Blocked,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4936,7 +5048,7 @@
         </is>
       </c>
       <c r="B2" s="19" t="n">
-        <v>46084</v>
+        <v>46077</v>
       </c>
       <c r="C2" s="17" t="inlineStr">
         <is>
@@ -4964,7 +5076,7 @@
         </is>
       </c>
       <c r="H2" s="19" t="n">
-        <v>46085</v>
+        <v>46078</v>
       </c>
       <c r="I2" s="17" t="inlineStr">
         <is>
@@ -4979,7 +5091,7 @@
         </is>
       </c>
       <c r="B3" s="19" t="n">
-        <v>46097</v>
+        <v>46090</v>
       </c>
       <c r="C3" s="17" t="inlineStr">
         <is>
@@ -5007,7 +5119,7 @@
         </is>
       </c>
       <c r="H3" s="19" t="n">
-        <v>46099</v>
+        <v>46092</v>
       </c>
       <c r="I3" s="17" t="inlineStr">
         <is>
@@ -5022,7 +5134,7 @@
         </is>
       </c>
       <c r="B4" s="19" t="n">
-        <v>46087</v>
+        <v>46080</v>
       </c>
       <c r="C4" s="17" t="inlineStr">
         <is>
@@ -5050,7 +5162,7 @@
         </is>
       </c>
       <c r="H4" s="19" t="n">
-        <v>46090</v>
+        <v>46083</v>
       </c>
       <c r="I4" s="17" t="inlineStr">
         <is>
@@ -5065,7 +5177,7 @@
         </is>
       </c>
       <c r="B5" s="19" t="n">
-        <v>46113</v>
+        <v>46106</v>
       </c>
       <c r="C5" s="17" t="inlineStr">
         <is>
@@ -5093,7 +5205,7 @@
         </is>
       </c>
       <c r="H5" s="19" t="n">
-        <v>46115</v>
+        <v>46108</v>
       </c>
       <c r="I5" s="17" t="inlineStr">
         <is>
@@ -5108,7 +5220,7 @@
         </is>
       </c>
       <c r="B6" s="19" t="n">
-        <v>46113</v>
+        <v>46106</v>
       </c>
       <c r="C6" s="17" t="inlineStr">
         <is>
@@ -5136,7 +5248,7 @@
         </is>
       </c>
       <c r="H6" s="19" t="n">
-        <v>46115</v>
+        <v>46108</v>
       </c>
       <c r="I6" s="17" t="inlineStr">
         <is>
@@ -5151,7 +5263,7 @@
         </is>
       </c>
       <c r="B7" s="19" t="n">
-        <v>46139</v>
+        <v>46132</v>
       </c>
       <c r="C7" s="17" t="inlineStr">
         <is>
@@ -5179,7 +5291,7 @@
         </is>
       </c>
       <c r="H7" s="19" t="n">
-        <v>46141</v>
+        <v>46134</v>
       </c>
       <c r="I7" s="17" t="inlineStr">
         <is>
@@ -5194,7 +5306,7 @@
         </is>
       </c>
       <c r="B8" s="19" t="n">
-        <v>46094</v>
+        <v>46087</v>
       </c>
       <c r="C8" s="17" t="inlineStr">
         <is>
@@ -5222,7 +5334,7 @@
         </is>
       </c>
       <c r="H8" s="19" t="n">
-        <v>46105</v>
+        <v>46098</v>
       </c>
       <c r="I8" s="17" t="inlineStr">
         <is>
@@ -5237,7 +5349,7 @@
         </is>
       </c>
       <c r="B9" s="19" t="n">
-        <v>46191</v>
+        <v>46185</v>
       </c>
       <c r="C9" s="17" t="inlineStr">
         <is>
@@ -5265,7 +5377,7 @@
         </is>
       </c>
       <c r="H9" s="19" t="n">
-        <v>46195</v>
+        <v>46189</v>
       </c>
       <c r="I9" s="17" t="inlineStr">
         <is>
@@ -5280,7 +5392,7 @@
         </is>
       </c>
       <c r="B10" s="19" t="n">
-        <v>46218</v>
+        <v>46212</v>
       </c>
       <c r="C10" s="17" t="inlineStr">
         <is>
@@ -5308,7 +5420,7 @@
         </is>
       </c>
       <c r="H10" s="19" t="n">
-        <v>46220</v>
+        <v>46216</v>
       </c>
       <c r="I10" s="17" t="inlineStr">
         <is>
@@ -5445,7 +5557,7 @@
         </is>
       </c>
       <c r="B2" s="19" t="n">
-        <v>46086</v>
+        <v>46079</v>
       </c>
       <c r="C2" s="17" t="inlineStr">
         <is>
@@ -5483,7 +5595,7 @@
         </is>
       </c>
       <c r="J2" s="19" t="n">
-        <v>46090</v>
+        <v>46083</v>
       </c>
     </row>
     <row r="3">
@@ -5493,7 +5605,7 @@
         </is>
       </c>
       <c r="B3" s="19" t="n">
-        <v>46121</v>
+        <v>46114</v>
       </c>
       <c r="C3" s="17" t="inlineStr">
         <is>
@@ -5531,7 +5643,7 @@
         </is>
       </c>
       <c r="J3" s="19" t="n">
-        <v>46132</v>
+        <v>46125</v>
       </c>
     </row>
     <row r="4">
@@ -5541,7 +5653,7 @@
         </is>
       </c>
       <c r="B4" s="19" t="n">
-        <v>46142</v>
+        <v>46135</v>
       </c>
       <c r="C4" s="17" t="inlineStr">
         <is>
@@ -5579,7 +5691,7 @@
         </is>
       </c>
       <c r="J4" s="19" t="n">
-        <v>46146</v>
+        <v>46139</v>
       </c>
     </row>
     <row r="5">
@@ -5589,7 +5701,7 @@
         </is>
       </c>
       <c r="B5" s="19" t="n">
-        <v>46168</v>
+        <v>46161</v>
       </c>
       <c r="C5" s="17" t="inlineStr">
         <is>
@@ -5627,7 +5739,7 @@
         </is>
       </c>
       <c r="J5" s="19" t="n">
-        <v>46170</v>
+        <v>46163</v>
       </c>
     </row>
   </sheetData>
@@ -5738,7 +5850,7 @@
         </is>
       </c>
       <c r="H2" s="19" t="n">
-        <v>46150</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="3">
@@ -5778,7 +5890,7 @@
         </is>
       </c>
       <c r="H3" s="19" t="n">
-        <v>46150</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="4">
@@ -5818,7 +5930,7 @@
         </is>
       </c>
       <c r="H4" s="19" t="n">
-        <v>46150</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="5">
@@ -5858,7 +5970,7 @@
         </is>
       </c>
       <c r="H5" s="19" t="n">
-        <v>46150</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="6">
@@ -5898,7 +6010,7 @@
         </is>
       </c>
       <c r="H6" s="19" t="n">
-        <v>46150</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="7">
@@ -5938,7 +6050,7 @@
         </is>
       </c>
       <c r="H7" s="19" t="n">
-        <v>46150</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="8">
@@ -5978,7 +6090,7 @@
         </is>
       </c>
       <c r="H8" s="19" t="n">
-        <v>46202</v>
+        <v>46196</v>
       </c>
     </row>
     <row r="9">
@@ -6018,7 +6130,7 @@
         </is>
       </c>
       <c r="H9" s="19" t="n">
-        <v>46150</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="10">
@@ -6058,7 +6170,7 @@
         </is>
       </c>
       <c r="H10" s="19" t="n">
-        <v>46150</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="11">
@@ -6098,7 +6210,7 @@
         </is>
       </c>
       <c r="H11" s="19" t="n">
-        <v>46132</v>
+        <v>46125</v>
       </c>
     </row>
   </sheetData>
@@ -6209,7 +6321,7 @@
         </is>
       </c>
       <c r="H2" s="19" t="n">
-        <v>46174</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="3">
@@ -6249,7 +6361,7 @@
         </is>
       </c>
       <c r="H3" s="19" t="n">
-        <v>46174</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="4">
@@ -6289,7 +6401,7 @@
         </is>
       </c>
       <c r="H4" s="19" t="n">
-        <v>46174</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="5">
@@ -6329,7 +6441,7 @@
         </is>
       </c>
       <c r="H5" s="19" t="n">
-        <v>46176</v>
+        <v>46169</v>
       </c>
     </row>
     <row r="6">
@@ -6369,7 +6481,7 @@
         </is>
       </c>
       <c r="H6" s="19" t="n">
-        <v>46177</v>
+        <v>46170</v>
       </c>
     </row>
     <row r="7">
@@ -6409,7 +6521,7 @@
         </is>
       </c>
       <c r="H7" s="19" t="n">
-        <v>46178</v>
+        <v>46171</v>
       </c>
     </row>
     <row r="8">
@@ -6449,7 +6561,7 @@
         </is>
       </c>
       <c r="H8" s="19" t="n">
-        <v>46175</v>
+        <v>46168</v>
       </c>
     </row>
     <row r="9">
@@ -6489,7 +6601,7 @@
         </is>
       </c>
       <c r="H9" s="19" t="n">
-        <v>46115</v>
+        <v>46108</v>
       </c>
     </row>
   </sheetData>
